--- a/backend/data/attachments/fund_Q3_2024_7.xlsx
+++ b/backend/data/attachments/fund_Q3_2024_7.xlsx
@@ -450,18 +450,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9561999999999999</v>
+        <v>1.3801</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3897</v>
+        <v>1.8372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>44651</v>
+        <v>18970</v>
       </c>
     </row>
     <row r="3">
@@ -471,18 +471,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.3901</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3997</v>
+        <v>1.8472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.793</t>
+          <t>0.835</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44751</v>
+        <v>19070</v>
       </c>
     </row>
     <row r="4">
@@ -492,18 +492,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9762</v>
+        <v>1.4001</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4097</v>
+        <v>1.8572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>-0.757</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44851</v>
+        <v>19170</v>
       </c>
     </row>
     <row r="5">
@@ -543,12 +543,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CATL</t>
+          <t>Kweichow Moutai</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
